--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending4(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending4(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_结局4（上）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="387">
   <si>
     <t>ID</t>
   </si>
@@ -423,6 +423,12 @@
     <t>话音刚落，他的声音便戛然而止。不是因为说完了，而是被什么东西打断了。</t>
   </si>
   <si>
+    <t>10 enhanced suspense</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music10)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=34</t>
   </si>
   <si>
@@ -456,12 +462,6 @@
     <t>源类型=type:txt_pb; 层级=37</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=38</t>
-  </si>
-  <si>
     <t>40</t>
   </si>
   <si>
@@ -661,6 +661,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -2417,7 +2422,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3760,7 +3765,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="36" ht="27" spans="1:12">
+    <row r="36" ht="30" spans="1:12">
       <c r="A36" t="s">
         <v>127</v>
       </c>
@@ -3786,21 +3791,21 @@
         <v>15</v>
       </c>
       <c r="I36" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="J36" t="s">
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="L36" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" ht="54" spans="1:12">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3818,7 +3823,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3830,15 +3835,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" ht="55.5" spans="1:12">
       <c r="A38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -3856,7 +3861,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -3871,12 +3876,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" ht="40.5" spans="1:12">
       <c r="A39" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -3894,7 +3899,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -3909,12 +3914,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="40" ht="40.5" spans="1:12">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" ht="54" spans="1:12">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -3932,7 +3937,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -3947,130 +3952,130 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="41" ht="54" spans="1:12">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41" t="s">
+        <v>15</v>
+      </c>
+      <c r="L41" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="42" ht="40.5" spans="1:12">
+      <c r="A42" t="s">
+        <v>148</v>
+      </c>
+      <c r="B42" t="s">
         <v>13</v>
       </c>
-      <c r="C41" t="s">
-        <v>14</v>
-      </c>
-      <c r="D41" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" t="s">
-        <v>143</v>
-      </c>
-      <c r="H41" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" t="s">
-        <v>15</v>
-      </c>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41" t="s">
-        <v>15</v>
-      </c>
-      <c r="L41" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" t="s">
-        <v>145</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s">
+        <v>149</v>
+      </c>
+      <c r="H42" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" t="s">
+        <v>15</v>
+      </c>
+      <c r="L42" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" t="s">
         <v>36</v>
       </c>
-      <c r="C42" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" t="s">
-        <v>15</v>
-      </c>
-      <c r="F42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" t="s">
-        <v>146</v>
-      </c>
-      <c r="H42" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" t="s">
-        <v>15</v>
-      </c>
-      <c r="J42" t="s">
-        <v>15</v>
-      </c>
-      <c r="K42" t="s">
-        <v>15</v>
-      </c>
-      <c r="L42" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" ht="40.5" spans="1:12">
-      <c r="A43" t="s">
-        <v>148</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s">
+        <v>152</v>
+      </c>
+      <c r="H43" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" t="s">
+        <v>15</v>
+      </c>
+      <c r="K43" t="s">
+        <v>15</v>
+      </c>
+      <c r="L43" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" ht="54" spans="1:12">
+      <c r="A44" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44" t="s">
         <v>13</v>
       </c>
-      <c r="C43" t="s">
-        <v>14</v>
-      </c>
-      <c r="D43" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" t="s">
-        <v>15</v>
-      </c>
-      <c r="F43" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" t="s">
-        <v>149</v>
-      </c>
-      <c r="H43" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" t="s">
-        <v>15</v>
-      </c>
-      <c r="J43" t="s">
-        <v>15</v>
-      </c>
-      <c r="K43" t="s">
-        <v>15</v>
-      </c>
-      <c r="L43" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" t="s">
-        <v>151</v>
-      </c>
-      <c r="B44" t="s">
-        <v>36</v>
-      </c>
       <c r="C44" t="s">
         <v>14</v>
       </c>
@@ -4084,7 +4089,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4096,15 +4101,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="L44" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="45" ht="54" spans="1:12">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="45" ht="42" spans="1:12">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4122,7 +4127,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4134,57 +4139,57 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="46" ht="42" spans="1:12">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B46" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s">
+        <v>163</v>
+      </c>
+      <c r="H46" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" t="s">
+        <v>15</v>
+      </c>
+      <c r="J46" t="s">
+        <v>15</v>
+      </c>
+      <c r="K46" t="s">
+        <v>15</v>
+      </c>
+      <c r="L46" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" ht="40.5" spans="1:12">
+      <c r="A47" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" t="s">
         <v>13</v>
       </c>
-      <c r="C46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" t="s">
-        <v>15</v>
-      </c>
-      <c r="F46" t="s">
-        <v>15</v>
-      </c>
-      <c r="G46" t="s">
-        <v>159</v>
-      </c>
-      <c r="H46" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" t="s">
-        <v>15</v>
-      </c>
-      <c r="J46" t="s">
-        <v>15</v>
-      </c>
-      <c r="K46" t="s">
-        <v>15</v>
-      </c>
-      <c r="L46" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" t="s">
-        <v>161</v>
-      </c>
-      <c r="B47" t="s">
-        <v>162</v>
-      </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
@@ -4198,7 +4203,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4213,12 +4218,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="48" ht="40.5" spans="1:12">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="48" ht="27" spans="1:12">
       <c r="A48" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4236,7 +4241,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4251,12 +4256,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="49" ht="27" spans="1:12">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" ht="55.5" spans="1:12">
       <c r="A49" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4274,7 +4279,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4286,15 +4291,15 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="L49" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="50" ht="55.5" spans="1:12">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="50" ht="27" spans="1:12">
       <c r="A50" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4312,7 +4317,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4324,171 +4329,171 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>173</v>
+        <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="51" ht="27" spans="1:12">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B51" t="s">
+        <v>179</v>
+      </c>
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" t="s">
+        <v>15</v>
+      </c>
+      <c r="K51" t="s">
+        <v>15</v>
+      </c>
+      <c r="L51" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="52" ht="54" spans="1:12">
+      <c r="A52" t="s">
+        <v>182</v>
+      </c>
+      <c r="B52" t="s">
         <v>13</v>
       </c>
-      <c r="C51" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51" t="s">
-        <v>176</v>
-      </c>
-      <c r="H51" t="s">
-        <v>15</v>
-      </c>
-      <c r="I51" t="s">
-        <v>15</v>
-      </c>
-      <c r="J51" t="s">
-        <v>15</v>
-      </c>
-      <c r="K51" t="s">
-        <v>15</v>
-      </c>
-      <c r="L51" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" t="s">
-        <v>178</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s">
+        <v>183</v>
+      </c>
+      <c r="H52" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" t="s">
+        <v>15</v>
+      </c>
+      <c r="J52" t="s">
+        <v>15</v>
+      </c>
+      <c r="K52" t="s">
+        <v>15</v>
+      </c>
+      <c r="L52" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" t="s">
+        <v>185</v>
+      </c>
+      <c r="B53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" t="s">
+        <v>15</v>
+      </c>
+      <c r="J53" t="s">
+        <v>15</v>
+      </c>
+      <c r="K53" t="s">
+        <v>15</v>
+      </c>
+      <c r="L53" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="54" ht="40.5" spans="1:12">
+      <c r="A54" t="s">
+        <v>188</v>
+      </c>
+      <c r="B54" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s">
+        <v>189</v>
+      </c>
+      <c r="H54" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" t="s">
+        <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54" t="s">
+        <v>15</v>
+      </c>
+      <c r="L54" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" ht="42" spans="1:12">
+      <c r="A55" t="s">
+        <v>191</v>
+      </c>
+      <c r="B55" t="s">
         <v>179</v>
       </c>
-      <c r="C52" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" t="s">
-        <v>15</v>
-      </c>
-      <c r="E52" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" t="s">
-        <v>15</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H52" t="s">
-        <v>15</v>
-      </c>
-      <c r="I52" t="s">
-        <v>15</v>
-      </c>
-      <c r="J52" t="s">
-        <v>15</v>
-      </c>
-      <c r="K52" t="s">
-        <v>15</v>
-      </c>
-      <c r="L52" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="53" ht="54" spans="1:12">
-      <c r="A53" t="s">
-        <v>182</v>
-      </c>
-      <c r="B53" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" t="s">
-        <v>14</v>
-      </c>
-      <c r="D53" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" t="s">
-        <v>15</v>
-      </c>
-      <c r="F53" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53" t="s">
-        <v>183</v>
-      </c>
-      <c r="H53" t="s">
-        <v>15</v>
-      </c>
-      <c r="I53" t="s">
-        <v>15</v>
-      </c>
-      <c r="J53" t="s">
-        <v>15</v>
-      </c>
-      <c r="K53" t="s">
-        <v>15</v>
-      </c>
-      <c r="L53" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12">
-      <c r="A54" t="s">
-        <v>185</v>
-      </c>
-      <c r="B54" t="s">
-        <v>36</v>
-      </c>
-      <c r="C54" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" t="s">
-        <v>15</v>
-      </c>
-      <c r="E54" t="s">
-        <v>15</v>
-      </c>
-      <c r="F54" t="s">
-        <v>15</v>
-      </c>
-      <c r="G54" t="s">
-        <v>186</v>
-      </c>
-      <c r="H54" t="s">
-        <v>15</v>
-      </c>
-      <c r="I54" t="s">
-        <v>15</v>
-      </c>
-      <c r="J54" t="s">
-        <v>15</v>
-      </c>
-      <c r="K54" t="s">
-        <v>15</v>
-      </c>
-      <c r="L54" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="55" ht="40.5" spans="1:12">
-      <c r="A55" t="s">
-        <v>188</v>
-      </c>
-      <c r="B55" t="s">
-        <v>13</v>
-      </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
@@ -4502,7 +4507,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4517,12 +4522,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="56" ht="42" spans="1:12">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" ht="55.5" spans="1:12">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B56" t="s">
         <v>179</v>
@@ -4540,7 +4545,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4555,54 +4560,54 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="57" ht="55.5" spans="1:12">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="57" ht="54" spans="1:12">
       <c r="A57" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B57" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s">
+        <v>198</v>
+      </c>
+      <c r="H57" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57" t="s">
+        <v>15</v>
+      </c>
+      <c r="K57" t="s">
+        <v>15</v>
+      </c>
+      <c r="L57" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="58" ht="57" spans="1:12">
+      <c r="A58" t="s">
+        <v>200</v>
+      </c>
+      <c r="B58" t="s">
         <v>179</v>
       </c>
-      <c r="C57" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57" t="s">
-        <v>15</v>
-      </c>
-      <c r="E57" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" t="s">
-        <v>195</v>
-      </c>
-      <c r="H57" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" t="s">
-        <v>15</v>
-      </c>
-      <c r="J57" t="s">
-        <v>15</v>
-      </c>
-      <c r="K57" t="s">
-        <v>15</v>
-      </c>
-      <c r="L57" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="58" ht="54" spans="1:12">
-      <c r="A58" t="s">
-        <v>197</v>
-      </c>
-      <c r="B58" t="s">
-        <v>13</v>
-      </c>
       <c r="C58" t="s">
         <v>14</v>
       </c>
@@ -4616,7 +4621,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4631,12 +4636,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="59" ht="57" spans="1:12">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="59" ht="42" spans="1:12">
       <c r="A59" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B59" t="s">
         <v>179</v>
@@ -4654,7 +4659,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4669,15 +4674,15 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="60" ht="42" spans="1:12">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="60" ht="27" spans="1:12">
       <c r="A60" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B60" t="s">
-        <v>179</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -4692,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4703,48 +4708,10 @@
       <c r="J60" t="s">
         <v>15</v>
       </c>
-      <c r="K60" t="s">
-        <v>15</v>
+      <c r="K60" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="L60" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="61" ht="27" spans="1:12">
-      <c r="A61" t="s">
-        <v>206</v>
-      </c>
-      <c r="B61" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61" t="s">
-        <v>207</v>
-      </c>
-      <c r="H61" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" t="s">
-        <v>15</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L61" t="s">
         <v>209</v>
       </c>
     </row>
